--- a/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_21-10-26.xlsx
+++ b/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_21-10-26.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21 Oct 2026 05:21 AM</t>
+          <t>21 Oct 2026 09:33 AM</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5259,7 +5259,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5323,7 +5323,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -16989,12 +16989,12 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -17090,12 +17090,12 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
